--- a/Gastos_Covenas.xlsx
+++ b/Gastos_Covenas.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimado" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesla" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carros" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4034,4 +4035,352 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>⛽ CARROS A GASOLINA — Medellín → Coveñas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Ruta, presupuesto y checklist para los 2 carros a gasolina del grupo. Mismos supuestos que la hoja 'Estimado' — investigado en foros de peajes y guías de viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>RUTA Y PARADAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Km aprox. desde Medellín</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Qué hacer ahí</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>0 km</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Salida</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Tanquear lleno antes de salir — evita buscar bomba con poco tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia / Caucasia</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>≈ 250 km</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Descanso + gasolina</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Punto medio natural, hay estaciones de servicio y sitios para comer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Planeta Rica / Sincelejo</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>≈ 350–400 km</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Gasolina si hace falta</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Segunda opción de tanqueo si no se llenó completo en Caucasia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>Coveñas / Tolú</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>≈ 500 km (destino)</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Llegada</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Confirmar parqueadero disponible en el condominio para los 2 carros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO POR CARRO (ida y vuelta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Cálculo</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Fuente / nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Gasolina (ida y vuelta)</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>≈500km ida x2 / 35 km-galón x $17.000/galón</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>486000</v>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>colombiapeajes.com / tarifas.info — rango real $340k-420k según rendimiento del carro</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Peajes (ida y vuelta)</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>≈$80.000 por trayecto x2</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>160000</v>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>colombiapeajes.com — ruta Medellín-Coveñas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Total estimado por carro (ida y vuelta):</t>
+        </is>
+      </c>
+      <c r="C15" s="28">
+        <f>SUM(C13:C14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Total 2 carros a gasolina:</t>
+        </is>
+      </c>
+      <c r="C16" s="28">
+        <f>C15*2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>CHECKLIST ANTES DE SALIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>☐  Revisión preventiva: llantas (incluida la de repuesto), frenos, aceite, luces, batería.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>☐  SOAT y tecnomecánica vigentes para la fecha del viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>☐  Kit de carretera: gato, cruceta, triángulos, chaleco reflectivo, botiquín, extintor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>☐  Tanquear lleno en Medellín antes de salir — no todas las paradas intermedias tienen bomba confiable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>☐  Coordinar con el otro carro un punto de encuentro fijo si se separan en el camino.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>☐  Llevar efectivo para peajes (algunos puntos de la ruta no tienen pago electrónico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>☐  Descansar cada 2-3 horas de manejo — son cerca de 9 horas de carretera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>☐  Guardar el recibo/soporte de gasolina y peajes si se va a repartir el gasto entre el carro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>FUENTES CONSULTADAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>—  colombiapeajes.com — peajes ruta Medellín-Coveñas</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>—  tarifas.info — gasolina y peajes Medellín-Coveñas 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>—  yotellevo.net / himmera.com — distancia y tiempo de viaje Medellín-Coveñas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Gastos_Covenas.xlsx
+++ b/Gastos_Covenas.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastos" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estimado" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesla" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carros" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carros" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tesla" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="$ #,##0"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,12 @@
     <font>
       <i val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B8863A"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -148,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -207,6 +213,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3345,7 +3354,7 @@
         </is>
       </c>
       <c r="B14" s="35">
-        <f>Tesla!C23</f>
+        <f>Tesla!C45</f>
         <v/>
       </c>
     </row>
@@ -3594,455 +3603,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>🔋 TESLA MODEL Y RWD — Medellín → Coveñas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>Ruta, paradas de carga, presupuesto y checklist para el carro de Andrés. Investigado en Club Tesla Colombia, guías de viaje en eléctrico a la costa Caribe y foros de carreteras — confirma disponibilidad real antes de salir, la red cambia seguido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>RUTA Y PARADAS DE CARGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="30" t="inlineStr">
-        <is>
-          <t>Parada</t>
-        </is>
-      </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>Km aprox. desde Medellín</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>Tipo de carga</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>Medellín (Unicentro, Laureles)</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>0 km</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
-        <is>
-          <t>Supercharger Tesla</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="inlineStr">
-        <is>
-          <t>Cargar al 100% aquí antes de salir. Es el Supercargador Tesla nativo más cercano al origen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>Caucasia</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>≈ 250 km</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>CCS Combo 2 (rápido)</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>Punto medio natural de la ruta. Requiere adaptador CCS — confirmar con Electromaps/Chargemap que esté operativo antes de salir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>Planeta Rica / Sincelejo</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>≈ 350–400 km</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>CCS Combo 2 (variable)</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>Alternativa si Caucasia no tiene el cargador disponible. Cobertura menos confiable, llevar margen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>Coveñas / Tolú</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>≈ 500 km (destino)</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Toma normal 110V (carga lenta) / variable</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>Confirmar con la propietaria si la cabaña tiene toma disponible para carga lenta overnight — evita depender de la red pública para el regreso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
-        <is>
-          <t>AUTONOMÍA Y CLIMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
-        <is>
-          <t>•  Model Y RWD: autonomía WLTP menor que la versión Long Range (~600 km) — cuenta con menos rango de sobra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
-        <is>
-          <t>•  En clima cálido (costa) la autonomía real baja entre 10% y 15% frente al valor de ficha, sobre todo usando aire acondicionado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="32" t="inlineStr">
-        <is>
-          <t>•  La topografía montañosa de la salida de Medellín también reduce el rendimiento — prevé más margen que en terreno plano.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="32" t="inlineStr">
-        <is>
-          <t>•  Con ≈500 km de trayecto y autonomía real probable de 350–400 km, es indispensable al menos 1 parada de carga por trayecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO DE CARGA (ida y vuelta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>Tramo</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="inlineStr">
-        <is>
-          <t>Estimado</t>
-        </is>
-      </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>Nota</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>Carga de salida en Medellín</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>Supercharger ($1.300/kWh)</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>Completar al 100% antes de salir</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Parada Caucasia (ida)</t>
-        </is>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>CCS Combo 2, carga parcial</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>Solo lo necesario para llegar a Coveñas</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Carga en destino (cabaña)</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Toma normal / lenta</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>Si la propietaria confirma toma disponible; tarifa doméstica, mucho más barata</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Parada Caucasia (regreso)</t>
-        </is>
-      </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>CCS Combo 2, carga parcial</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Para volver a Medellín con margen</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Total estimado carga Tesla (ida y vuelta):</t>
-        </is>
-      </c>
-      <c r="C23" s="28">
-        <f>SUM(C19:C22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
-        <is>
-          <t>Nota: mucho más barato que un carro a gasolina en el mismo trayecto (~$466.000 ida y vuelta en gasolina+peajes, ver hoja 'Estimado'). El supuesto 'Carga Tesla ida y vuelta' de la hoja Estimado está ligado a este total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>CHECKLIST ANTES DE SALIR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>☐  Cargar al 100% en el Supercargador de Unicentro Medellín la noche o mañana antes de salir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>☐  Llevar el adaptador CCS Combo 2 — la mayoría de cargadores rápidos en Colombia usan ese estándar, no el conector Tesla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>☐  Instalar Electromaps o Chargemap y confirmar el día del viaje qué cargadores de Caucasia/Sincelejo están operativos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>☐  Llevar el cable/cargador portátil (mobile connector) por si toca cargar lento en una toma normal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>☐  Revisión preventiva antes de carretera: llantas, frenos, sistema de refrigeración de batería.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>☐  Activar modo Eco y aprovechar el frenado regenerativo; usar el aire acondicionado a temperatura media, no al máximo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>☐  No conectar a cargar apenas se llega bajo sol fuerte — dejar que la batería se estabilice unos minutos primero.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>☐  En Coveñas, evitar dejar el carro parqueado directo al sol del mediodía por horas largas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>☐  Confirmar con la propietaria de la cabaña si hay una toma 110V disponible para cargar lento durante la estadía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>☐  Tener un plan B (ruta o parada alterna) si algún cargador de la lista aparece fuera de servicio ese día.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>FUENTES CONSULTADAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>—  Club Tesla Colombia — guía de cargadores y adaptadores, tarifa Supercharger ($1.300/kWh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>—  BYD Colombia — ruta y paradas de carga hacia la Costa Caribe (incluye zona Coveñas–Tolú)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="34" t="inlineStr">
-        <is>
-          <t>—  Pulzo / El Espectador / Carroya — cuidado de batería en calor y viajes largos en eléctrico</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>—  La República / El Tiempo — mapa de estaciones de carga en Colombia</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A24:D25"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A14:D14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4383,4 +3943,776 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🔋 TESLA MODEL Y RWD — Medellín → Coveñas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Actualizado con reportes REALES de la comunidad Tesla Colombia Motors Club (grupos de WhatsApp 'Viajes' y 'Viajes y Rutas 🛣️') — gente que ya hizo esta ruta o una muy parecida, no solo estimaciones web. Andrés ya había cotizado esta misma ruta ahí antes de este viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>LA DECISIÓN: RUTA POR MONTERÍA (no por Sincelejo/Fátima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>La comunidad (bot 'Optimus' de teslacolombiamotorsclub.com + Andrés mismo cotizando esta ruta) comparó las dos rutas posibles. La de Montería gana claro: es 140 km más corta y necesita la MITAD de paradas de carga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Distancia ida</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Paradas de carga (ida)</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>Paradas de carga (regreso)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>✅ Por Montería (RECOMENDADA) — Medellín → Caucasia → Montería → Coveñas</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>≈492 km</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>1 (Caucasia)</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>1 (Caucasia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>Por Sincelejo — Medellín → Caucasia → Fátima → Sincelejo → Coveñas</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>≈634 km</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>2 (Fátima + Sincelejo)</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>2 (Sincelejo + Fátima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>CARGADORES CONFIRMADOS (reportados por conductores reales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Punto de carga</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>Lo que reportó la comunidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>Terpel Voltex Popalito</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Barbosa, salida de Medellín</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>CCS2 rápido</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Primera parada típica saliendo de Medellín. Varios reportes la usan para salir con carga completa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>Terpel Voltex Caucasia</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Caucasia (≈284 km de Medellín)</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>CCS2 rápido</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Parada obligatoria en la ruta por Montería, ida y vuelta. Es la única parada necesaria si vas por esta ruta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>Terpel Voltex Fátima</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Cerca de Buenavista, ≈50 km después de Caucasia</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>CCS2, nominal 40-50 kW</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>⚠️ Reportes de la comunidad: a veces entrega solo 20 kW por calor extremo (40°C) — una carga que debería tomar 25-30 min tomó 2 horas. Solo se usa en la ruta por Sincelejo, no en la de Montería.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>Places Mall — Montería</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Centro comercial Places Mall, Montería</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>Confirmado con fotos por la comunidad</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>Parada opcional de margen en la ruta por Montería — no es obligatoria si sales de Caucasia con buena carga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>Terpel Voltex Sincelejo</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>CCS2 rápido</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Existe (un miembro de la comunidad corrigió al bot, que inicialmente decía que no había nada en Sincelejo). Solo aplica a la ruta alterna por Sincelejo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>EPM Los Álamos</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Carrera 52 #65-07, Medellín</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>CCS2 + CHAdeMO + Tipo 2</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Alternativa en Medellín para cargar al 100% antes de salir. Nota de la comunidad: algunos cargadores EPM solo funcionan con tarjeta física, no con la app — llévala por si acaso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>AUTONOMÍA REAL (no la de ficha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>•  Ficha técnica (WLTP): 466 km. Reportado por la comunidad en condiciones normales: 380-420 km reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>•  Para esta ruta específica (calor, humedad, A/C, velocidad de carretera), el cálculo de la comunidad da ≈353 km de autonomía usable — más conservador que el WLTP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>•  Con 491-492 km de distancia, NO alcanza sin cargar aunque toda la ruta sea de bajada (Medellín 1493m → Coveñas 4m). Cotizado y confirmado varias veces por el bot de la comunidad para esta ruta exacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>•  El Model Y RWD gasta 10-15% más que el AWD en el mismo trayecto — si algún día viaja alguien con AWD, sus números son más holgados que los de acá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>⚠️ EL REGRESO ES MÁS DIFÍCIL QUE LA IDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>La ida es bajada (Medellín 1493m → Coveñas 4m) y gasta poco. El regreso sube por Caucasia de nuevo a 1300m+ y gasta 30-40% MÁS energía que la ida en ese mismo tramo. Un conductor real reportó llegar de vuelta a Barbosa con apenas 5% de batería. Carga a 90-95% en Caucasia antes de subir, no al 80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>PLAN RECOMENDADO (ruta por Montería)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>Tramo</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Distancia</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Salida</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Llegada estimada</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>IDA — Medellín → Caucasia</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>284 km</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>100% (cargado en Medellín)</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>≈20-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>Carga en Caucasia</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>20-25%</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>→ 90-95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>IDA — Caucasia → Montería → Coveñas</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>208 km</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>≈50-55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>En Coveñas</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>≈50-55%</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>Cargar AC lenta en la cabaña si hay toma disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>REGRESO — Coveñas → Caucasia</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>208 km</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>50-55% (o más si cargó en la cabaña)</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>≈25-30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>Carga en Caucasia (regreso)</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>25-30%</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>→ 90-95% — OBLIGATORIA antes de la subida</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>REGRESO — Caucasia → Medellín (subida)</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>284 km</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>90-95%</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>≈15-25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO DE CARGA (ida y vuelta, ruta por Montería)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Tramo</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Estimado</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Carga de salida en Medellín</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Terpel Voltex / EPM Los Álamos</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>Completar al 100% antes de salir</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Carga en Caucasia (ida)</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>Terpel Voltex, ~20%→90%</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>Única parada necesaria en la ida por Montería</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Carga en la cabaña (Coveñas)</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>AC lenta / toma 110-220V</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>Si la propietaria confirma toma disponible — negociar esto con tiempo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>Carga en Caucasia (regreso)</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>Terpel Voltex, carga a 90-95%</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>65000</v>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>Obligatoria — la subida a Medellín no perdona</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Total estimado carga Tesla (ida y vuelta):</t>
+        </is>
+      </c>
+      <c r="C45" s="28">
+        <f>SUM(C41:C44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>CHECKLIST ANTES DE SALIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>☐  Cargar al 100% en Medellín (Terpel Voltex Popalito o EPM Los Álamos) antes de salir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>☐  Confirmar con Electromaps/PlugShare/Terpel App que el cargador de Caucasia está operativo el día del viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>☐  ⚠️ El viaje es en temporada de puente/fin de año — los cargadores de la ruta pueden estar más congestionados de lo normal. Un miembro de la comunidad canceló su viaje por esto mismo en un festivo. Salir temprano y tener plan B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>☐  Llevar tarjeta física de EPM además de la app (algunos cargadores EPM no funcionan solo con app).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>☐  Llevar adaptador CCS1→CCS2 y cable/cargador portátil (mobile connector) para toma normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>☐  Confirmar CON TIEMPO con la propietaria de la cabaña si hay una toma 110V/220V disponible para cargar lento durante la estadía — define si el regreso es tranquilo o ajustado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>☐  En Caucasia (ida y vuelta), cargar a 90-95%, no solo al 80% — el tramo de subida en el regreso no da margen para quedarse corto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>☐  Cuidado si se lleva el carro a la orilla de la playa — la arena y la salitre no son amigas de los EVs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>☐  Usar la app ABRP (A Better Route Planner) o el navegador de Tesla para ir monitoreando el % real en vivo durante el viaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>☐  Después del viaje, considerar registrarlo en teslacolombiamotorsclub.com/tecnico/viajes — ayuda a la comunidad con datos reales de esta ruta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="21" t="inlineStr">
+        <is>
+          <t>FUENTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>—  Grupo de WhatsApp 'Viajes' (Tesla Colombia Motors Club) — Andrés cotizó esta misma ruta ahí varias veces (mayo-julio 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>—  Grupo de WhatsApp 'Viajes y Rutas 🛣️' — reportes reales de viajeros que hicieron Medellín-Costa Caribe en Model Y RWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>—  Bot 'Optimus' (teslacolombiamotorsclub.com) — cálculos de ruta con ciclo EVRL + ruteo OSRM, corregidos con datos de la comunidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>—  Reporte real de viaje: Medellín → Popalito → Caucasia → Fátima → Cartagena (Model Y RWD, junio 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>—  Reporte real: Medellín → Coveñas vía Cereté/Lorica (Jorge Londoño, vía @superacorrea, julio 2026)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A26:D27"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>